--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA130"/>
+  <dimension ref="A1:AA132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14628,6 +14628,232 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>23690</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>9 Saltoniškių gatvė</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>08105</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>arturas@baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>303346220</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baltas-dobilas/</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baltasdobilas/</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baltasdobilas</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@baltasdobilas4047</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>Artūras Vasilionok</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/art%C5%ABras-vasilionok-b2b38798/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>23690</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>9 Saltoniškių gatvė</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>08105</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>arturas@baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>303346220</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baltas-dobilas/</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baltasdobilas/</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baltasdobilas</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@baltasdobilas4047</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Mantas Paulius</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mantas-paulius-171a8298/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA132"/>
+  <dimension ref="A1:AA134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14854,6 +14854,232 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>23690</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>9 Saltoniškių gatvė</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>08105</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>arturas@baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>303346220</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baltas-dobilas/</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baltasdobilas/</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baltasdobilas</t>
+        </is>
+      </c>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@baltasdobilas4047</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Artūras Vasilionok</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/art%C5%ABras-vasilionok-b2b38798/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Baltas Dobilas Uab</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>23690</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>9 Saltoniškių gatvė</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>08105</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>arturas@baltasdobilas.com</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>303346220</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/baltas-dobilas/</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/baltasdobilas/</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baltasdobilas</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@baltasdobilas4047</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Mantas Paulius</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>Import Manager</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mantas-paulius-171a8298/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA134"/>
+  <dimension ref="A1:AA138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15080,6 +15080,362 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>167679</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Kaunas</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Energetikų g. 46</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>52485</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osama.lt</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>info@osama.lt</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+370 37 352404</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osama-uab</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100072350779597</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uab_osama/</t>
+        </is>
+      </c>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Irmantas Kinderis</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/irmantas-kinderis-3786b517a</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>167679</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Kaunas</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Energetikų g. 46</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>52485</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osama.lt</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>info@osama.lt</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>+370 37 352404</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osama-uab</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100072350779597</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uab_osama/</t>
+        </is>
+      </c>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>Rimantas Siniauskas</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rimantas-siniauskas-43887211b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>167679</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Kaunas</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Energetikų g. 46</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>52485</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osama.lt</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>info@osama.lt</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>+370 37 352404</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr"/>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osama-uab</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100072350779597</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uab_osama/</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>Rekstys Vaidas</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rekstys-vaidas-04267643/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>167679</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Kaunas</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Energetikų g. 46</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>52485</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osama.lt</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>info@osama.lt</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>+370 37 352404</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/osama-uab</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100072350779597</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uab_osama/</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>Edita V.</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/editavirviciene/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA138"/>
+  <dimension ref="A1:AA142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15436,6 +15436,442 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>103879</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2B Metalo gatvė</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>02190</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>http://www.amberdistribution.lt, https://www.amberdrinks.lt</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>lithuania@amberbev.com</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>+370 800 77 000</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>110365450</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amber-distribution-lithuania/</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AmberDrinksLT</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdrinkslt/</t>
+        </is>
+      </c>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>Žydrūnas Krapukaitis</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Category Manager (Wine and Sparkling wine)</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zkrapukaitis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>103879</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2B Metalo gatvė</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>02190</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>http://www.amberdistribution.lt, https://www.amberdrinks.lt</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>lithuania@amberbev.com</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>+370 800 77 000</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>110365450</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amber-distribution-lithuania/</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AmberDrinksLT</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdrinkslt/</t>
+        </is>
+      </c>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>Mantas Butautas</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mantas-butautas-22936124a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>103879</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>2B Metalo gatvė</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>02190</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>http://www.amberdistribution.lt, https://www.amberdrinks.lt</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>lithuania@amberbev.com</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>+370 800 77 000</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>110365450</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amber-distribution-lithuania/</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AmberDrinksLT</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdrinkslt/</t>
+        </is>
+      </c>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>Rasa Bakasėnaitė</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Manager</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rasa-bakas%C4%97nait%C4%97-699277173/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Lithuania Uab</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>103879</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2B Metalo gatvė</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>02190</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>http://www.amberdistribution.lt, https://www.amberdrinks.lt</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>lithuania@amberbev.com</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>+370 800 77 000</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>110365450</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amber-distribution-lithuania/</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AmberDrinksLT</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdrinkslt/</t>
+        </is>
+      </c>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>Oksana Valentinovic</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Manager</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oksana-valentinovic-41982041/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA142"/>
+  <dimension ref="A1:AA143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15872,6 +15872,87 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Maža Pilis Uab</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Maža Pilis Uab</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>103881</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis, Vilniaus miesto savivaldybė</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>43 Kazimiero Jelskio gatvę</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>04132</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mazapilis.lt</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>info@mazapilis.lt</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>Ruslanas Kraučenka</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ruslanas-krau%C4%8Denka-33b4a511/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA143"/>
+  <dimension ref="A1:AA145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15953,6 +15953,208 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr"/>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>Domantas Lekys</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales Lithuania, Business Development Baltics</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domantas-lekys-b831383a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Peleda</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-peleda-7494978b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA145"/>
+  <dimension ref="A1:AA147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16155,6 +16155,208 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr"/>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>Domantas Lekys</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales Lithuania, Business Development Baltics</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domantas-lekys-b831383a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr"/>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Peleda</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-peleda-7494978b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA147"/>
+  <dimension ref="A1:AA149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16357,6 +16357,208 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>Domantas Lekys</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales Lithuania, Business Development Baltics</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domantas-lekys-b831383a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr"/>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Peleda</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-peleda-7494978b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA149"/>
+  <dimension ref="A1:AA151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16559,6 +16559,208 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr"/>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Domantas Lekys</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales Lithuania, Business Development Baltics</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domantas-lekys-b831383a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr"/>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Peleda</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-peleda-7494978b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Lithuania.xlsx
+++ b/BWI/bestwine_output/bestwine_Lithuania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA151"/>
+  <dimension ref="A1:AA153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16761,6 +16761,208 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr"/>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Domantas Lekys</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sales Lithuania, Business Development Baltics</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/domantas-lekys-b831383a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>3b Solutions Uab</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>49677</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Vilnius</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus apskritis</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Laisvės Pr. 3</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>04215</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.3bsolutions.lt</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>info@3bs.lt</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>+370 5 203 1355</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>302310253</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3bsolution/</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr"/>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Peleda</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-peleda-7494978b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
